--- a/documents/useful/temperature sensor converter.xlsx
+++ b/documents/useful/temperature sensor converter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Programming\gauge.s-sorek.uk\documents\useful\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D21709-1D4D-44B1-95DC-63C9F639A667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD5DF7A4-0AE5-4CED-A780-0810286897B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-15" windowWidth="30495" windowHeight="21135" firstSheet="7" activeTab="11" xr2:uid="{B7E37433-98C9-4AC7-A732-162F4F4FFF98}"/>
+    <workbookView xWindow="-120" yWindow="-15" windowWidth="30495" windowHeight="21015" firstSheet="9" activeTab="13" xr2:uid="{B7E37433-98C9-4AC7-A732-162F4F4FFF98}"/>
   </bookViews>
   <sheets>
     <sheet name="Bosch 0280130026 oil temp" sheetId="11" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="27 NPT 3-160 pressure" sheetId="18" r:id="rId10"/>
     <sheet name="Beta (osculati)" sheetId="19" r:id="rId11"/>
     <sheet name="Bosch E36 coolant sensor (2)" sheetId="21" r:id="rId12"/>
+    <sheet name="VDO S50 12611404699 801 37 2" sheetId="23" r:id="rId13"/>
+    <sheet name="AEM" sheetId="24" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2321" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2608" uniqueCount="117">
   <si>
     <t>Voltage (V)</t>
   </si>
@@ -149,6 +151,255 @@
   </si>
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>Temp C</t>
+  </si>
+  <si>
+    <t>-20 C</t>
+  </si>
+  <si>
+    <t>-10 C</t>
+  </si>
+  <si>
+    <t>0C</t>
+  </si>
+  <si>
+    <t>10 C</t>
+  </si>
+  <si>
+    <t>20 C</t>
+  </si>
+  <si>
+    <t>30 C</t>
+  </si>
+  <si>
+    <t>40 C</t>
+  </si>
+  <si>
+    <t>50 C</t>
+  </si>
+  <si>
+    <t>60 C</t>
+  </si>
+  <si>
+    <t>70 C</t>
+  </si>
+  <si>
+    <t>80 C</t>
+  </si>
+  <si>
+    <t>90 C</t>
+  </si>
+  <si>
+    <t>100 C</t>
+  </si>
+  <si>
+    <t>110 C</t>
+  </si>
+  <si>
+    <t>120 C</t>
+  </si>
+  <si>
+    <t>130 C</t>
+  </si>
+  <si>
+    <t>140 C</t>
+  </si>
+  <si>
+    <t>150 C</t>
+  </si>
+  <si>
+    <t>Temp F</t>
+  </si>
+  <si>
+    <t>-4 F</t>
+  </si>
+  <si>
+    <t>14 F</t>
+  </si>
+  <si>
+    <t>32 F</t>
+  </si>
+  <si>
+    <t>50 F</t>
+  </si>
+  <si>
+    <t>68 F</t>
+  </si>
+  <si>
+    <t>86 F</t>
+  </si>
+  <si>
+    <t>104 F</t>
+  </si>
+  <si>
+    <t>122 F</t>
+  </si>
+  <si>
+    <t>140 F</t>
+  </si>
+  <si>
+    <t>158 F</t>
+  </si>
+  <si>
+    <t>176 F</t>
+  </si>
+  <si>
+    <t>194 F</t>
+  </si>
+  <si>
+    <t>212 F</t>
+  </si>
+  <si>
+    <t>230 F</t>
+  </si>
+  <si>
+    <t>248 F</t>
+  </si>
+  <si>
+    <t>266 F</t>
+  </si>
+  <si>
+    <t>284 F</t>
+  </si>
+  <si>
+    <t>302 F</t>
+  </si>
+  <si>
+    <t>Calibration</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Resistance</t>
+  </si>
+  <si>
+    <t>Ohms</t>
+  </si>
+  <si>
+    <t>Voltage with 5v Pull-Up Resistor</t>
+  </si>
+  <si>
+    <t>S1, S2, &amp; AQ1</t>
+  </si>
+  <si>
+    <t>2,200 Ohms</t>
+  </si>
+  <si>
+    <t>4.64 Volts</t>
+  </si>
+  <si>
+    <t>4.39 Volts</t>
+  </si>
+  <si>
+    <t>4.05 Volts</t>
+  </si>
+  <si>
+    <t>3.59 Volts</t>
+  </si>
+  <si>
+    <t>3.06 Volts</t>
+  </si>
+  <si>
+    <t>2.52 Volts</t>
+  </si>
+  <si>
+    <t>2.00 Volts</t>
+  </si>
+  <si>
+    <t>1.55 Volts</t>
+  </si>
+  <si>
+    <t>1.17 Volts</t>
+  </si>
+  <si>
+    <t>0.88 Volts</t>
+  </si>
+  <si>
+    <t>0.66 Volts</t>
+  </si>
+  <si>
+    <t>0.49 Volts</t>
+  </si>
+  <si>
+    <t>0.37 Volts</t>
+  </si>
+  <si>
+    <t>0.28 Volts</t>
+  </si>
+  <si>
+    <t>0.21 Volts</t>
+  </si>
+  <si>
+    <t>0.16 Volts</t>
+  </si>
+  <si>
+    <t>0.13 Volts</t>
+  </si>
+  <si>
+    <t>0.10 Volts</t>
+  </si>
+  <si>
+    <t>Infinity ECU</t>
+  </si>
+  <si>
+    <t>2,490 Ohms</t>
+  </si>
+  <si>
+    <t>4.59 Volts</t>
+  </si>
+  <si>
+    <t>4.32 Volts</t>
+  </si>
+  <si>
+    <t>3.95 Volts</t>
+  </si>
+  <si>
+    <t>3.46 Volts</t>
+  </si>
+  <si>
+    <t>2.91 Volts</t>
+  </si>
+  <si>
+    <t>2.36 Volts</t>
+  </si>
+  <si>
+    <t>1.85 Volts</t>
+  </si>
+  <si>
+    <t>1.42 Volts</t>
+  </si>
+  <si>
+    <t>1.06 Volts</t>
+  </si>
+  <si>
+    <t>0.79 Volts</t>
+  </si>
+  <si>
+    <t>0.59 Volts</t>
+  </si>
+  <si>
+    <t>0.44 Volts</t>
+  </si>
+  <si>
+    <t>0.33 Volts</t>
+  </si>
+  <si>
+    <t>0.25 Volts</t>
+  </si>
+  <si>
+    <t>0.19 Volts</t>
+  </si>
+  <si>
+    <t>0.14 Volts</t>
+  </si>
+  <si>
+    <t>0.11 Volts</t>
+  </si>
+  <si>
+    <t>0.08 Volts</t>
   </si>
 </sst>
 </file>
@@ -355,7 +606,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -417,6 +668,12 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3095,6 +3352,1196 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'VDO S50 12611404699 801 37 2'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Temperature (°C)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.5234547115180995E-2"/>
+                  <c:y val="-0.47986147066810153"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y </a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t>= -8.9368x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="30000">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t>3</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t> + 51.392x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="30000">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t>2</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t> - 143.25x + 235.45</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 1</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln w="31750">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'VDO S50 12611404699 801 37 2'!$D$2:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.80529180526156641</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.46738197424892702</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.38737864077669903</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33370786516853934</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25290858725761772</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.19324044436076065</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.14964200477326969</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.11620839363241678</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.2691223636893749E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.4508845665135381E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6.0259179265658748E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'VDO S50 12611404699 801 37 2'!$G$2:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E818-4B69-BE24-D41EF64E341D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="5"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.21466134090070507"/>
+                  <c:y val="-0.73754440590189851"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln w="31750">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'VDO S50 12611404699 801 37 2'!$F$2:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.51440988989762404</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30770613922424866</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25689884531474483</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22239618788291357</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16980781153130814</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13046538234852251</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.10144138843947639</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.9023648346405018E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6.3170730238635731E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0865933479323756E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.1193122887508704E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'VDO S50 12611404699 801 37 2'!$G$2:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>150</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E818-4B69-BE24-D41EF64E341D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="646701888"/>
+        <c:axId val="789408384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="646701888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="789408384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="789408384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="646701888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Bosch E36 coolant sensor (2)'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Temperature (°C)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.5234547115180995E-2"/>
+                  <c:y val="-0.47986147066810153"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>y </a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t>= -8.9368x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="30000">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t>3</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t> + 51.392x</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="30000">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t>2</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                        <a:effectLst/>
+                      </a:rPr>
+                      <a:t> - 143.25x + 235.45</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 1</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln w="31750">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Bosch E36 coolant sensor (2)'!$D$2:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>2.8478832716810518</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.6792325056433408</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.4791044776119402</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2550348321722606</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0154534838458544</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7722222222222221</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.5352941176470589</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.3180180180180181</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.1217821782178219</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.95124555160142343</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.80566893424036268</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Bosch E36 coolant sensor (2)'!$G$2:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>37.777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.888888888888886</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71.111111111111114</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.222222222222229</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93.333333333333329</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>104.44444444444444</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115.55555555555556</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>126.66666666666667</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>137.77777777777777</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>148.88888888888889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-616A-4844-BC7A-6967EC0CCF75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="5"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.21466134090070507"/>
+                  <c:y val="-0.73754440590189851"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln w="31750">
+                  <a:solidFill>
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="60000"/>
+                      <a:lumOff val="40000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Bosch E36 coolant sensor (2)'!$F$2:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1.5420504589321482</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4692111482051089</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.3803324099722991</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2775269904432627</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1635518600992869</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0433102081268582</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.92153487014881807</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.80558985483063561</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69716576542979669</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.5999387880024486</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.51463371812316205</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Bosch E36 coolant sensor (2)'!$G$2:$G$12</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>37.777777777777779</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.888888888888886</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>71.111111111111114</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>82.222222222222229</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>93.333333333333329</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>104.44444444444444</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>115.55555555555556</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>126.66666666666667</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>137.77777777777777</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>148.88888888888889</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-616A-4844-BC7A-6967EC0CCF75}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="646701888"/>
+        <c:axId val="789408384"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="646701888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="789408384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="789408384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="646701888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -8736,6 +10183,86 @@
 </file>
 
 <file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -11159,6 +12686,1038 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -15435,6 +17994,92 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E408446B-F6D2-4267-8C23-17466C459213}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>347382</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76123434-A44D-4E4E-90CA-016453955CA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>347382</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>800100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77F20335-413A-41B5-867C-C74518303CF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -19685,7 +22330,7 @@
         <v>3.25</v>
       </c>
       <c r="B71" s="18">
-        <f t="shared" ref="B71:B102" si="2">1/(1/$B$3 * LN((($B$4*A71)/($B$5-A71))/$B$2)+1/($B$1+273.15)) - 273.15</f>
+        <f t="shared" ref="B71" si="2">1/(1/$B$3 * LN((($B$4*A71)/($B$5-A71))/$B$2)+1/($B$1+273.15)) - 273.15</f>
         <v>-46.839474542638158</v>
       </c>
     </row>
@@ -20500,6 +23145,2298 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733DADA3-F08D-4452-B58D-3731F9ED0507}">
+  <dimension ref="A1:AD48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" style="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="2"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="2"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>3.3</v>
+      </c>
+      <c r="C2" s="29">
+        <v>322.8</v>
+      </c>
+      <c r="D2" s="10">
+        <f>($B$2*C2)/($A$2+C2)</f>
+        <v>0.80529180526156641</v>
+      </c>
+      <c r="E2" s="9">
+        <f>C2*($A$6+$A$7)/(C2+$A$6+$A$7)</f>
+        <v>293.22130123765186</v>
+      </c>
+      <c r="F2" s="11">
+        <f>(($B$2*E2)/($B$6+E2))*$A$6/($A$6+$A$7)</f>
+        <v>0.51440988989762404</v>
+      </c>
+      <c r="G2" s="29">
+        <v>50</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="4">
+        <f>D2</f>
+        <v>0.80529180526156641</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="12">
+        <f>G2</f>
+        <v>50</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>F2</f>
+        <v>0.51440988989762404</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="12">
+        <f>G2</f>
+        <v>50</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C3" s="29">
+        <v>165</v>
+      </c>
+      <c r="D3" s="10">
+        <f t="shared" ref="D3:D11" si="0">($B$2*C3)/($A$2+C3)</f>
+        <v>0.46738197424892702</v>
+      </c>
+      <c r="E3" s="9">
+        <f t="shared" ref="E3:E12" si="1">C3*($A$6+$A$7)/(C3+$A$6+$A$7)</f>
+        <v>156.90936106983656</v>
+      </c>
+      <c r="F3" s="11">
+        <f>(($B$2*E3)/($B$6+E3))*$A$6/($A$6+$A$7)</f>
+        <v>0.30770613922424866</v>
+      </c>
+      <c r="G3" s="29">
+        <v>60</v>
+      </c>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T3" s="4">
+        <f t="shared" ref="T3:T12" si="2">D3</f>
+        <v>0.46738197424892702</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="12">
+        <f t="shared" ref="W3:W12" si="3">G3</f>
+        <v>60</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z3" s="4">
+        <f t="shared" ref="Z3:Z12" si="4">F3</f>
+        <v>0.30770613922424866</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="12">
+        <f t="shared" ref="AC3:AC12" si="5">G3</f>
+        <v>60</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="29">
+        <v>133</v>
+      </c>
+      <c r="D4" s="10">
+        <f t="shared" si="0"/>
+        <v>0.38737864077669903</v>
+      </c>
+      <c r="E4" s="9">
+        <f t="shared" si="1"/>
+        <v>127.69276927692769</v>
+      </c>
+      <c r="F4" s="11">
+        <f>(($B$2*E4)/($B$6+E4))*$A$6/($A$6+$A$7)</f>
+        <v>0.25689884531474483</v>
+      </c>
+      <c r="G4" s="29">
+        <v>70</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" s="4">
+        <f t="shared" si="2"/>
+        <v>0.38737864077669903</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W4" s="12">
+        <f t="shared" si="3"/>
+        <v>70</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="4"/>
+        <v>0.25689884531474483</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="12">
+        <f t="shared" si="5"/>
+        <v>70</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="29">
+        <v>112.5</v>
+      </c>
+      <c r="D5" s="10">
+        <f>($B$2*C5)/($A$2+C5)</f>
+        <v>0.33370786516853934</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="1"/>
+        <v>108.67924528301887</v>
+      </c>
+      <c r="F5" s="11">
+        <f>(($B$2*E5)/($B$6+E5))*$A$6/($A$6+$A$7)</f>
+        <v>0.22239618788291357</v>
+      </c>
+      <c r="G5" s="29">
+        <v>80</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T5" s="4">
+        <f t="shared" si="2"/>
+        <v>0.33370786516853934</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="12">
+        <f t="shared" si="3"/>
+        <v>80</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="4"/>
+        <v>0.22239618788291357</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="12">
+        <f t="shared" si="5"/>
+        <v>80</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2200</v>
+      </c>
+      <c r="B6">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="29">
+        <v>83</v>
+      </c>
+      <c r="D6" s="10">
+        <f>($B$2*C6)/($A$2+C6)</f>
+        <v>0.25290858725761772</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" si="1"/>
+        <v>80.90161437709412</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" ref="F6:F11" si="6">(($B$2*E6)/($B$6+E6))*$A$6/($A$6+$A$7)</f>
+        <v>0.16980781153130814</v>
+      </c>
+      <c r="G6" s="29">
+        <v>90</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T6" s="4">
+        <f t="shared" si="2"/>
+        <v>0.25290858725761772</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" s="12">
+        <f t="shared" si="3"/>
+        <v>90</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="4"/>
+        <v>0.16980781153130814</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="12">
+        <f t="shared" si="5"/>
+        <v>90</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="29">
+        <v>62.2</v>
+      </c>
+      <c r="D7" s="10">
+        <f>($B$2*C7)/($A$2+C7)</f>
+        <v>0.19324044436076065</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="1"/>
+        <v>61.014039605174425</v>
+      </c>
+      <c r="F7" s="11">
+        <f>(($B$2*E7)/($B$6+E7))*$A$6/($A$6+$A$7)</f>
+        <v>0.13046538234852251</v>
+      </c>
+      <c r="G7" s="29">
+        <v>100</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T7" s="4">
+        <f t="shared" si="2"/>
+        <v>0.19324044436076065</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W7" s="12">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="4"/>
+        <v>0.13046538234852251</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="12">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C8" s="29">
+        <v>47.5</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="0"/>
+        <v>0.14964200477326969</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="1"/>
+        <v>46.805234795996924</v>
+      </c>
+      <c r="F8" s="11">
+        <f>(($B$2*E8)/($B$6+E8))*$A$6/($A$6+$A$7)</f>
+        <v>0.10144138843947639</v>
+      </c>
+      <c r="G8" s="29">
+        <v>110</v>
+      </c>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="4">
+        <f t="shared" si="2"/>
+        <v>0.14964200477326969</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <f t="shared" si="3"/>
+        <v>110</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="4"/>
+        <v>0.10144138843947639</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="12">
+        <f t="shared" si="5"/>
+        <v>110</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C9" s="29">
+        <v>36.5</v>
+      </c>
+      <c r="D9" s="10">
+        <f t="shared" si="0"/>
+        <v>0.11620839363241678</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="1"/>
+        <v>36.088367063185537</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="6"/>
+        <v>7.9023648346405018E-2</v>
+      </c>
+      <c r="G9" s="29">
+        <v>120</v>
+      </c>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="4">
+        <f t="shared" si="2"/>
+        <v>0.11620839363241678</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W9" s="12">
+        <f t="shared" si="3"/>
+        <v>120</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="4"/>
+        <v>7.9023648346405018E-2</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="12">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C10" s="29">
+        <v>28.9</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="0"/>
+        <v>9.2691223636893749E-2</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="1"/>
+        <v>28.641332961689738</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="6"/>
+        <v>6.3170730238635731E-2</v>
+      </c>
+      <c r="G10" s="29">
+        <v>130</v>
+      </c>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="4">
+        <f t="shared" si="2"/>
+        <v>9.2691223636893749E-2</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W10" s="12">
+        <f t="shared" si="3"/>
+        <v>130</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="4"/>
+        <v>6.3170730238635731E-2</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="12">
+        <f t="shared" si="5"/>
+        <v>130</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C11" s="29">
+        <v>23.1</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="0"/>
+        <v>7.4508845665135381E-2</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="1"/>
+        <v>22.934441996835346</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="6"/>
+        <v>5.0865933479323756E-2</v>
+      </c>
+      <c r="G11" s="29">
+        <v>140</v>
+      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="4">
+        <f t="shared" si="2"/>
+        <v>7.4508845665135381E-2</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="12">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="4"/>
+        <v>5.0865933479323756E-2</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="12">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C12" s="29">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="D12" s="10">
+        <f>($B$2*C12)/($A$2+C12)</f>
+        <v>6.0259179265658748E-2</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="1"/>
+        <v>18.492512272416583</v>
+      </c>
+      <c r="F12" s="11">
+        <f>(($B$2*E12)/($B$6+E12))*$A$6/($A$6+$A$7)</f>
+        <v>4.1193122887508704E-2</v>
+      </c>
+      <c r="G12" s="29">
+        <v>150</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="4">
+        <f t="shared" si="2"/>
+        <v>6.0259179265658748E-2</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W12" s="12">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="4"/>
+        <v>4.1193122887508704E-2</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="12">
+        <f t="shared" si="5"/>
+        <v>150</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="S13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T13" s="4"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="12"/>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C15" s="9"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C16" s="9"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="19" spans="13:26" x14ac:dyDescent="0.25">
+      <c r="M19" s="5"/>
+    </row>
+    <row r="22" spans="13:26" x14ac:dyDescent="0.25">
+      <c r="M22" s="1"/>
+    </row>
+    <row r="24" spans="13:26" x14ac:dyDescent="0.25">
+      <c r="T24"/>
+      <c r="Z24"/>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+    </row>
+    <row r="44" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+    </row>
+    <row r="45" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+    </row>
+    <row r="46" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+    </row>
+    <row r="47" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+    </row>
+    <row r="48" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1418CD25-7625-40B6-92BC-22083E9958EB}">
+  <dimension ref="A1:AD142"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" style="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S1" s="2"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="2"/>
+      <c r="AB1" s="2"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="2"/>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <v>3.3</v>
+      </c>
+      <c r="C2">
+        <v>28136</v>
+      </c>
+      <c r="D2" s="10">
+        <f>($B$2*C2)/($A$2+C2)</f>
+        <v>3.1867380560131791</v>
+      </c>
+      <c r="E2" s="9">
+        <f>C2*($A$6+$A$7)/(C2+$A$6+$A$7)</f>
+        <v>2873.2193004850651</v>
+      </c>
+      <c r="F2" s="11">
+        <f>(($B$2*E2)/($B$6+E2))*$A$6/($A$6+$A$7)</f>
+        <v>1.6829969547965249</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-4</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="4">
+        <f>D2</f>
+        <v>3.1867380560131791</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="12">
+        <f>G2</f>
+        <v>-4</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z2" s="4">
+        <f>F2</f>
+        <v>1.6829969547965249</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" s="12">
+        <f>G2</f>
+        <v>-4</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>15813</v>
+      </c>
+      <c r="D3" s="10">
+        <f t="shared" ref="D3:D11" si="0">($B$2*C3)/($A$2+C3)</f>
+        <v>3.1037233093439598</v>
+      </c>
+      <c r="E3" s="9">
+        <f t="shared" ref="E3:E12" si="1">C3*($A$6+$A$7)/(C3+$A$6+$A$7)</f>
+        <v>2661.4211329090622</v>
+      </c>
+      <c r="F3" s="11">
+        <f>(($B$2*E3)/($B$6+E3))*$A$6/($A$6+$A$7)</f>
+        <v>1.6491135480200994</v>
+      </c>
+      <c r="G3" s="10">
+        <v>14</v>
+      </c>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T3" s="4">
+        <f t="shared" ref="T3:T12" si="2">D3</f>
+        <v>3.1037233093439598</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="12">
+        <f t="shared" ref="W3:W12" si="3">G3</f>
+        <v>14</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z3" s="4">
+        <f t="shared" ref="Z3:Z12" si="4">F3</f>
+        <v>1.6491135480200994</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="12">
+        <f t="shared" ref="AC3:AC12" si="5">G3</f>
+        <v>14</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>9319</v>
+      </c>
+      <c r="D4" s="10">
+        <f t="shared" si="0"/>
+        <v>2.9802015699195654</v>
+      </c>
+      <c r="E4" s="9">
+        <f t="shared" si="1"/>
+        <v>2382.043294192827</v>
+      </c>
+      <c r="F4" s="11">
+        <f>(($B$2*E4)/($B$6+E4))*$A$6/($A$6+$A$7)</f>
+        <v>1.5979277181280969</v>
+      </c>
+      <c r="G4" s="10">
+        <v>32</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" s="4">
+        <f t="shared" si="2"/>
+        <v>2.9802015699195654</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W4" s="12">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z4" s="4">
+        <f t="shared" si="4"/>
+        <v>1.5979277181280969</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC4" s="12">
+        <f t="shared" si="5"/>
+        <v>32</v>
+      </c>
+      <c r="AD4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>5589</v>
+      </c>
+      <c r="D5" s="10">
+        <f>($B$2*C5)/($A$2+C5)</f>
+        <v>2.7991652754590985</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="1"/>
+        <v>2034.9072704517009</v>
+      </c>
+      <c r="F5" s="11">
+        <f>(($B$2*E5)/($B$6+E5))*$A$6/($A$6+$A$7)</f>
+        <v>1.5211983294468725</v>
+      </c>
+      <c r="G5" s="10">
+        <v>50</v>
+      </c>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T5" s="4">
+        <f t="shared" si="2"/>
+        <v>2.7991652754590985</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="12">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="4">
+        <f t="shared" si="4"/>
+        <v>1.5211983294468725</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC5" s="12">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2200</v>
+      </c>
+      <c r="B6">
+        <v>1000</v>
+      </c>
+      <c r="C6">
+        <v>3476</v>
+      </c>
+      <c r="D6" s="10">
+        <f>($B$2*C6)/($A$2+C6)</f>
+        <v>2.5627345844504021</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" si="1"/>
+        <v>1666.1473936488915</v>
+      </c>
+      <c r="F6" s="11">
+        <f t="shared" ref="F6:F11" si="6">(($B$2*E6)/($B$6+E6))*$A$6/($A$6+$A$7)</f>
+        <v>1.4178030473279699</v>
+      </c>
+      <c r="G6" s="10">
+        <v>68</v>
+      </c>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T6" s="4">
+        <f t="shared" si="2"/>
+        <v>2.5627345844504021</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W6" s="12">
+        <f t="shared" si="3"/>
+        <v>68</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="4"/>
+        <v>1.4178030473279699</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC6" s="12">
+        <f t="shared" si="5"/>
+        <v>68</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1000</v>
+      </c>
+      <c r="C7">
+        <v>2230</v>
+      </c>
+      <c r="D7" s="10">
+        <f>($B$2*C7)/($A$2+C7)</f>
+        <v>2.278328173374613</v>
+      </c>
+      <c r="E7" s="9">
+        <f t="shared" si="1"/>
+        <v>1314.1804788213628</v>
+      </c>
+      <c r="F7" s="11">
+        <f>(($B$2*E7)/($B$6+E7))*$A$6/($A$6+$A$7)</f>
+        <v>1.2883813464905298</v>
+      </c>
+      <c r="G7" s="10">
+        <v>86</v>
+      </c>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T7" s="4">
+        <f t="shared" si="2"/>
+        <v>2.278328173374613</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W7" s="12">
+        <f t="shared" si="3"/>
+        <v>86</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="4">
+        <f t="shared" si="4"/>
+        <v>1.2883813464905298</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="12">
+        <f t="shared" si="5"/>
+        <v>86</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>1466</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="0"/>
+        <v>1.961800486618005</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" si="1"/>
+        <v>1005.4007715387912</v>
+      </c>
+      <c r="F8" s="11">
+        <f>(($B$2*E8)/($B$6+E8))*$A$6/($A$6+$A$7)</f>
+        <v>1.1374300004274782</v>
+      </c>
+      <c r="G8" s="10">
+        <v>104</v>
+      </c>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="4">
+        <f t="shared" si="2"/>
+        <v>1.961800486618005</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="12">
+        <f t="shared" si="3"/>
+        <v>104</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="4">
+        <f t="shared" si="4"/>
+        <v>1.1374300004274782</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC8" s="12">
+        <f t="shared" si="5"/>
+        <v>104</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>984</v>
+      </c>
+      <c r="D9" s="10">
+        <f t="shared" si="0"/>
+        <v>1.6366935483870966</v>
+      </c>
+      <c r="E9" s="9">
+        <f t="shared" si="1"/>
+        <v>752.58126195028683</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="6"/>
+        <v>0.97423085315295654</v>
+      </c>
+      <c r="G9" s="10">
+        <v>122</v>
+      </c>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="4">
+        <f t="shared" si="2"/>
+        <v>1.6366935483870966</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W9" s="12">
+        <f t="shared" si="3"/>
+        <v>122</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="4">
+        <f t="shared" si="4"/>
+        <v>0.97423085315295654</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC9" s="12">
+        <f t="shared" si="5"/>
+        <v>122</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>671</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="0"/>
+        <v>1.3251346499102332</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" si="1"/>
+        <v>554.68871092740892</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="6"/>
+        <v>0.80945465421554597</v>
+      </c>
+      <c r="G10" s="10">
+        <v>140</v>
+      </c>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="4">
+        <f t="shared" si="2"/>
+        <v>1.3251346499102332</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W10" s="12">
+        <f t="shared" si="3"/>
+        <v>140</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="4">
+        <f t="shared" si="4"/>
+        <v>0.80945465421554597</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" s="12">
+        <f t="shared" si="5"/>
+        <v>140</v>
+      </c>
+      <c r="AD10" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>468</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="0"/>
+        <v>1.0520435967302451</v>
+      </c>
+      <c r="E11" s="9">
+        <f t="shared" si="1"/>
+        <v>408.2878953107961</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="6"/>
+        <v>0.65775127768313457</v>
+      </c>
+      <c r="G11" s="10">
+        <v>158</v>
+      </c>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" s="4">
+        <f t="shared" si="2"/>
+        <v>1.0520435967302451</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="12">
+        <f t="shared" si="3"/>
+        <v>158</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="4">
+        <f t="shared" si="4"/>
+        <v>0.65775127768313457</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC11" s="12">
+        <f t="shared" si="5"/>
+        <v>158</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>332</v>
+      </c>
+      <c r="D12" s="10">
+        <f>($B$2*C12)/($A$2+C12)</f>
+        <v>0.82252252252252245</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" si="1"/>
+        <v>300.79275198187997</v>
+      </c>
+      <c r="F12" s="11">
+        <f>(($B$2*E12)/($B$6+E12))*$A$6/($A$6+$A$7)</f>
+        <v>0.52462127807765979</v>
+      </c>
+      <c r="G12" s="10">
+        <v>176</v>
+      </c>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="4">
+        <f t="shared" si="2"/>
+        <v>0.82252252252252245</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="W12" s="12">
+        <f t="shared" si="3"/>
+        <v>176</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="4">
+        <f t="shared" si="4"/>
+        <v>0.52462127807765979</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC12" s="12">
+        <f t="shared" si="5"/>
+        <v>176</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>239</v>
+      </c>
+      <c r="D13" s="10">
+        <f t="shared" ref="D13:D19" si="7">($B$2*C13)/($A$2+C13)</f>
+        <v>0.63656174334140425</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" ref="E13:E19" si="8">C13*($A$6+$A$7)/(C13+$A$6+$A$7)</f>
+        <v>222.39022971794125</v>
+      </c>
+      <c r="F13" s="11">
+        <f t="shared" ref="F13:F19" si="9">(($B$2*E13)/($B$6+E13))*$A$6/($A$6+$A$7)</f>
+        <v>0.41275512631428701</v>
+      </c>
+      <c r="G13" s="10">
+        <v>194</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="T13" s="4"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="12"/>
+      <c r="AD13" s="2"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C14">
+        <v>175</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="7"/>
+        <v>0.49148936170212765</v>
+      </c>
+      <c r="E14" s="9">
+        <f t="shared" si="8"/>
+        <v>165.92592592592592</v>
+      </c>
+      <c r="F14" s="11">
+        <f t="shared" si="9"/>
+        <v>0.32287166454891997</v>
+      </c>
+      <c r="G14" s="10">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>129</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="7"/>
+        <v>0.37705934455270151</v>
+      </c>
+      <c r="E15" s="9">
+        <f t="shared" si="8"/>
+        <v>124.00120156203064</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="9"/>
+        <v>0.25029130365064939</v>
+      </c>
+      <c r="G15" s="10">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>97</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" si="7"/>
+        <v>0.29179580674566996</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="8"/>
+        <v>94.146193509250836</v>
+      </c>
+      <c r="F16" s="11">
+        <f t="shared" si="9"/>
+        <v>0.19521539058601761</v>
+      </c>
+      <c r="G16" s="10">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>73</v>
+      </c>
+      <c r="D17" s="10">
+        <f t="shared" si="7"/>
+        <v>0.22451071761416586</v>
+      </c>
+      <c r="E17" s="9">
+        <f t="shared" si="8"/>
+        <v>71.371830125267337</v>
+      </c>
+      <c r="F17" s="11">
+        <f t="shared" si="9"/>
+        <v>0.15113785433183141</v>
+      </c>
+      <c r="G17" s="10">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>57</v>
+      </c>
+      <c r="D18" s="10">
+        <f t="shared" si="7"/>
+        <v>0.17795648060548722</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="8"/>
+        <v>56.002456248081053</v>
+      </c>
+      <c r="F18" s="11">
+        <f t="shared" si="9"/>
+        <v>0.12031749723789034</v>
+      </c>
+      <c r="G18" s="10">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>43</v>
+      </c>
+      <c r="D19" s="10">
+        <f t="shared" si="7"/>
+        <v>0.13604985618408438</v>
+      </c>
+      <c r="E19" s="9">
+        <f t="shared" si="8"/>
+        <v>42.429848905334566</v>
+      </c>
+      <c r="F19" s="11">
+        <f t="shared" si="9"/>
+        <v>9.2344554221144168E-2</v>
+      </c>
+      <c r="G19" s="10">
+        <v>302</v>
+      </c>
+      <c r="M19" s="5"/>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="M22" s="1"/>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.25">
+      <c r="T24"/>
+      <c r="Z24"/>
+    </row>
+    <row r="36" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N51" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N54" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N55" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N57" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N58" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N59" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N60" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N61" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="62" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N62" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="63" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N63" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="64" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N64" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N65" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N66" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N68" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N69" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N70" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N71" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N72" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N73" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N74" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N75" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N79" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N81" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N82">
+        <v>28136</v>
+      </c>
+    </row>
+    <row r="83" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N83">
+        <v>15813</v>
+      </c>
+    </row>
+    <row r="84" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N84">
+        <v>9319</v>
+      </c>
+    </row>
+    <row r="85" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N85">
+        <v>5589</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N86">
+        <v>3476</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N87">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="88" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N88">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="89" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N89">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="90" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N90">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="91" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N91">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="92" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N92">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="93" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N93">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N94">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="95" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N95">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="96" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N96">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="97" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N97">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="98" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N98">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="99" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N99">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="101" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N101" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="102" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N102" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N103" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N104" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N105" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N106" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="107" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N107" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="108" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N108" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="109" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N109" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="110" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N110" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="111" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N111" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N112" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N113" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="114" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N114" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N115" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N116" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N117" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N118" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N119" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="120" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N120" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="121" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N121" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="123" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N123" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="124" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N124" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="125" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N125" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="126" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N126" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N127" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N128" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="129" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N129" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="130" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N130" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="131" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N131" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="132" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N132" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="133" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N133" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="134" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N134" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="135" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N135" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="136" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N136" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="137" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N137" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="138" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N138" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="139" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N139" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="140" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N140" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="141" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N141" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="142" spans="14:14" x14ac:dyDescent="0.25">
+      <c r="N142" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
